--- a/output/fwreq1.xlsx
+++ b/output/fwreq1.xlsx
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Firmware Update – Secure Boot Enhancement</t>
+          <t>Firmware Power Management – Adaptive Sleep Mode Enhancement</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,42 +501,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Power Management</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement enhanced secure boot validation in firmware to ensure only signed and trusted firmware images are executed during device startup.</t>
+          <t>Implement an adaptive sleep mode in firmware that dynamically adjusts power states based on device activity and user patterns.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Prevents unauthorized or malicious firmware from running, reducing security risks and ensuring compliance with enterprise security standards.</t>
+          <t>Reduces overall power consumption, extends device lifespan, and supports sustainability goals.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Improved device security, reduced risk of firmware attacks, and increased customer trust in device integrity.</t>
+          <t>Lower energy costs for customers and improved device reliability through smarter power management.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>End users should not notice any change in device behavior; boot process remains seamless.</t>
+          <t>Device should seamlessly enter and exit sleep mode without noticeable delay or disruption to the user.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Applies to all new firmware releases for Victoria platform devices.</t>
+          <t>Firmware-level changes to support adaptive sleep logic across all supported device models.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Firmware must reject unsigned images and log validation failures.</t>
+          <t>Device enters sleep mode within 2 minutes of inactivity and wakes in under 5 seconds.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Zero successful boot attempts with unsigned or tampered firmware.</t>
+          <t>Device enters sleep mode within 1 minute of inactivity and wakes in under 2 seconds.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -546,69 +546,69 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Secure key management infrastructure; Firmware signing tools</t>
+          <t>Device activity monitoring subsystem; Power state controller</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Firmware Development</t>
+          <t>Firmware team; Hardware engineering</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power Management – Sleep Mode Optimization</t>
+          <t>Security – Firmware Update Authentication</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Emily Chen</t>
+          <t>Priya Patel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Optimize firmware sleep mode to reduce power consumption during device idle periods without impacting wake-up performance.</t>
+          <t>Require cryptographic authentication for all firmware updates to prevent unauthorized code execution.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Extends device battery life and meets energy efficiency targets for enterprise customers.</t>
+          <t>Protects devices from malicious firmware and ensures only trusted updates are applied.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lower operational costs and improved sustainability metrics for customers.</t>
+          <t>Reduces risk of security breaches and maintains customer trust in device integrity.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Device should enter and exit sleep mode quickly and reliably, with no user-perceived delays.</t>
+          <t>Firmware updates should proceed only if authentication passes, with clear error messaging on failure.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Victoria platform devices in all supported configurations.</t>
+          <t>All firmware update mechanisms, including OTA and USB-based updates.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sleep mode power consumption ≤ 0.5W; wake-up time ≤ 2 seconds.</t>
+          <t>All firmware updates must be signed and verified before installation.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sleep mode power consumption ≤ 0.3W; wake-up time ≤ 1 second.</t>
+          <t>Zero unauthenticated firmware updates allowed in the field.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,69 +618,69 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Power management IC; System BIOS</t>
+          <t>Cryptographic library; Update delivery infrastructure</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Hardware Engineering; Power Systems Team</t>
+          <t>Security team; Firmware update service</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Network Stack – IPv6 Support</t>
+          <t>Diagnostics – Enhanced Error Logging</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
+          <t>Alex Chen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Connectivity</t>
+          <t>Diagnostics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Add IPv6 protocol support to the firmware network stack to enable modern network compatibility.</t>
+          <t>Expand firmware error logging to include detailed event traces and error codes for all critical subsystems.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ensures future-proofing and compatibility with enterprise and ISP networks transitioning to IPv6.</t>
+          <t>Improves troubleshooting efficiency and reduces time to resolution for field issues.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Expanded market reach and compliance with customer network requirements.</t>
+          <t>Faster support response and reduced device downtime for customers.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Network connectivity should be seamless for both IPv4 and IPv6 environments.</t>
+          <t>Error logs should be accessible via standard diagnostic tools and clearly indicate root causes.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Victoria platform devices with network capability.</t>
+          <t>All critical firmware subsystems, including power, connectivity, and storage.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Basic IPv6 connectivity verified in lab environments.</t>
+          <t>Critical errors are logged with timestamps and subsystem identifiers.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Full IPv6 feature parity with existing IPv4 stack.</t>
+          <t>All errors include event traces and actionable error codes.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Network driver updates; QA test cases for IPv6</t>
+          <t>Logging framework; Diagnostic tool integration</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Network Engineering; QA Team</t>
+          <t>Support engineering; QA</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -819,52 +819,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Firmware Update – Secure Boot Enhancement</t>
+          <t>Firmware Power Management – Adaptive Sleep Mode</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Alex Kim</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Power Management</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Implement enhanced secure boot functionality in firmware to prevent unauthorized code execution during device startup.</t>
+          <t>Implement an adaptive sleep mode in firmware that dynamically adjusts power states based on device activity and usage patterns.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Addresses critical security vulnerabilities and aligns with industry standards for device protection.</t>
+          <t>Reduces overall energy consumption and extends device lifespan, aligning with corporate sustainability goals.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reduces risk of firmware-level attacks, improves customer trust, and meets compliance requirements.</t>
+          <t>Lower operational costs for customers and improved device reliability through smarter power management.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Device should boot only trusted firmware images, with no user disruption.</t>
+          <t>Device should seamlessly enter and exit sleep mode without noticeable delay or disruption to user workflows.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Applies to all new devices in the Victoria program; does not affect legacy models.</t>
+          <t>Firmware-level changes to support adaptive sleep transitions; applies to all supported device models.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Secure boot enabled by default; no unsigned code execution.</t>
+          <t>Device enters sleep mode within 2 minutes of inactivity and wakes in under 5 seconds.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Zero successful unauthorized boot attempts in validation testing.</t>
+          <t>Optimize power usage to achieve at least 10% reduction in standby energy consumption.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Secure key provisioning; firmware signing infrastructure</t>
+          <t>Device activity monitoring subsystem; hardware power state support</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Security Engineering; Platform Firmware Team</t>
+          <t>Firmware Engineering; Hardware Platform Team</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>

--- a/output/fwreq1.xlsx
+++ b/output/fwreq1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Firmware Power Management – Adaptive Sleep Mode Enhancement</t>
+          <t>Firmware Update – Add Secure Boot Support</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,42 +501,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Power Management</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement an adaptive sleep mode in firmware that dynamically adjusts power states based on device activity and user patterns.</t>
+          <t>Implement Secure Boot functionality in the firmware to ensure only signed and trusted code is executed during the boot process.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reduces overall power consumption, extends device lifespan, and supports sustainability goals.</t>
+          <t>Addresses increasing security threats and aligns with industry standards for device integrity.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lower energy costs for customers and improved device reliability through smarter power management.</t>
+          <t>Reduces risk of malware at boot, improves customer trust, and meets compliance requirements.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Device should seamlessly enter and exit sleep mode without noticeable delay or disruption to the user.</t>
+          <t>Device should boot only when firmware integrity is verified.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Firmware-level changes to support adaptive sleep logic across all supported device models.</t>
+          <t>All new platforms launching in 2025; does not apply to legacy models.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Device enters sleep mode within 2 minutes of inactivity and wakes in under 5 seconds.</t>
+          <t>Secure Boot enabled and verified on all supported platforms.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Device enters sleep mode within 1 minute of inactivity and wakes in under 2 seconds.</t>
+          <t>Zero unsigned code execution during boot.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -546,24 +546,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Device activity monitoring subsystem; Power state controller</t>
+          <t>Platform hardware support for Secure Boot; signing infrastructure</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Firmware team; Hardware engineering</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MUST</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Security – Firmware Update Authentication</t>
+          <t>Power Management – Deep Sleep Mode Enhancement</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -573,42 +573,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Require cryptographic authentication for all firmware updates to prevent unauthorized code execution.</t>
+          <t>Enhance deep sleep mode to reduce standby power consumption below 0.5W.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Protects devices from malicious firmware and ensures only trusted updates are applied.</t>
+          <t>Improves energy efficiency and supports sustainability goals.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reduces risk of security breaches and maintains customer trust in device integrity.</t>
+          <t>Lower energy costs for customers and improved ENERGY STAR compliance.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Firmware updates should proceed only if authentication passes, with clear error messaging on failure.</t>
+          <t>Device should wake instantly from deep sleep without user-perceptible delay.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>All firmware update mechanisms, including OTA and USB-based updates.</t>
+          <t>Applies to all desktop platforms with Intel 13th Gen CPUs.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>All firmware updates must be signed and verified before installation.</t>
+          <t>Standby power consumption ≤ 0.5W in deep sleep.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Zero unauthenticated firmware updates allowed in the field.</t>
+          <t>Standby power consumption ≤ 0.3W.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -618,24 +618,24 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cryptographic library; Update delivery infrastructure</t>
+          <t>Intel 13th Gen CPU firmware support; power delivery subsystem</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Security team; Firmware update service</t>
+          <t>Platform Power Team; Intel</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diagnostics – Enhanced Error Logging</t>
+          <t>Firmware Logging – Expand Event Log Capacity</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,37 +650,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Expand firmware error logging to include detailed event traces and error codes for all critical subsystems.</t>
+          <t>Increase firmware event log capacity from 128 to 512 entries.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Improves troubleshooting efficiency and reduces time to resolution for field issues.</t>
+          <t>Enables better post-mortem analysis and reduces lost diagnostic data.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Faster support response and reduced device downtime for customers.</t>
+          <t>Improved support experience and faster root cause analysis.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Error logs should be accessible via standard diagnostic tools and clearly indicate root causes.</t>
+          <t>Technicians should always have access to recent event history.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All critical firmware subsystems, including power, connectivity, and storage.</t>
+          <t>All commercial platforms shipping in 2024 and beyond.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Critical errors are logged with timestamps and subsystem identifiers.</t>
+          <t>Firmware event log supports at least 512 entries.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>All errors include event traces and actionable error codes.</t>
+          <t>No event loss during typical 3-month usage window.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Logging framework; Diagnostic tool integration</t>
+          <t>Firmware storage allocation; event log parser updates</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Support engineering; QA</t>
+          <t>Diagnostics Team; Firmware Storage Team</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Firmware Power Management – Adaptive Sleep Mode</t>
+          <t>Firmware Update – Add Secure Boot Support</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -829,42 +829,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Power Management</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Implement an adaptive sleep mode in firmware that dynamically adjusts power states based on device activity and usage patterns.</t>
+          <t>Implement Secure Boot functionality in the firmware to ensure only signed and trusted firmware images are executed during the boot process.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Reduces overall energy consumption and extends device lifespan, aligning with corporate sustainability goals.</t>
+          <t>Addresses increasing security threats and aligns with industry standards for device integrity.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lower operational costs for customers and improved device reliability through smarter power management.</t>
+          <t>Reduces risk of unauthorized firmware execution, improves compliance posture, and increases customer trust.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Device should seamlessly enter and exit sleep mode without noticeable delay or disruption to user workflows.</t>
+          <t>End users should not notice any change in boot experience unless an unauthorized firmware is detected, in which case a clear error message is displayed.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Firmware-level changes to support adaptive sleep transitions; applies to all supported device models.</t>
+          <t>Applies to all new platforms launching with Victoria and any existing platforms that can support Secure Boot via firmware update.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Device enters sleep mode within 2 minutes of inactivity and wakes in under 5 seconds.</t>
+          <t>Secure Boot enabled by default on all supported platforms; blocks unsigned firmware.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Optimize power usage to achieve at least 10% reduction in standby energy consumption.</t>
+          <t>Zero unsigned firmware allowed to execute; error handling for failed verification.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -874,17 +874,89 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Device activity monitoring subsystem; hardware power state support</t>
+          <t>Platform hardware support for Secure Boot; signed firmware image infrastructure.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Firmware Engineering; Hardware Platform Team</t>
+          <t>Security Architecture; Platform Firmware Team; Manufacturing</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MUST</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Thermal Management – Adaptive Fan Control Algorithm</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Priya Desai</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Thermal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Develop and integrate an adaptive fan control algorithm that dynamically adjusts fan speed based on real-time thermal sensor data.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Improves device reliability and user comfort by optimizing thermal performance and reducing noise.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Extends hardware lifespan, reduces RMA rates, and enhances end-user satisfaction through quieter operation.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Users should experience quieter device operation under typical workloads without thermal throttling.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>All Victoria-based platforms with active cooling systems.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Fan speed dynamically adjusts to maintain CPU temperature below 80°C under standard workloads.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Maintain CPU temperature below 75°C in 95% of use cases; minimize fan noise.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Thermal sensor integration; firmware fan control module.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Thermal Engineering; Platform Firmware; Hardware Design</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>

--- a/output/fwreq1.xlsx
+++ b/output/fwreq1.xlsx
@@ -413,550 +413,1340 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Requestor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Requirement (What)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Justification (Why)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>New Threshold (Acceptable to Ship)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Target (Design Goal)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Requestors</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>What is it?</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Strategic Importance of Solution</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Value Proposition</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Experience Intent (if any)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>New Threshold (Acceptable to Ship)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Target (Design Goal)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Impacted Programs</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Partners</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Priority</t>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>conversion_status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Firmware Update – Add Secure Boot Support</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Rajesh Kumar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Power Management</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Implement Secure Boot functionality in the firmware to ensure only signed and trusted code is executed during the boot process.</t>
+          <t>API response time should be under 2 seconds</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Addresses increasing security threats and aligns with industry standards for device integrity.</t>
+          <t>Improve user experience and reduce latency</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of malware at boot, improves customer trust, and meets compliance requirements.</t>
+          <t>Device enters sleep mode within 2 minutes of inactivity and wakes within 5 seconds.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Device should boot only when firmware integrity is verified.</t>
+          <t>Device enters sleep mode within 1 minute of inactivity and wakes within 2 seconds.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>All new platforms launching in 2025; does not apply to legacy models.</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all supported platforms.</t>
+          <t>Firmware-level power state management for all supported device models.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Zero unsigned code execution during boot.</t>
+          <t>Firmware</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>Firmware Power Management – Adaptive Sleep Mode</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Alex Kim</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Implement an adaptive sleep mode in firmware that dynamically adjusts power states based on device activity and usage patterns.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Reduces overall power consumption, extends device lifespan, and supports sustainability goals.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Lower energy costs for end users and improved device reliability through reduced wear.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Device should seamlessly enter and exit sleep mode without noticeable delay or disruption to the user.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Victoria</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Platform hardware support for Secure Boot; signing infrastructure</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Security Engineering; Platform Firmware Team</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>MUST</t>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Device activity monitoring subsystem; hardware power state support</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Firmware team; Hardware engineering</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Power Management – Deep Sleep Mode Enhancement</t>
-        </is>
+      <c r="A3" t="n">
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Sneha Reddy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Enhance deep sleep mode to reduce standby power consumption below 0.5W.</t>
+          <t>Implement multi-factor authentication</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Improves energy efficiency and supports sustainability goals.</t>
+          <t>Enhance system security</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lower energy costs for customers and improved ENERGY STAR compliance.</t>
+          <t>Device rejects unsigned firmware images during boot.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Device should wake instantly from deep sleep without user-perceptible delay.</t>
+          <t>Zero successful unauthorized firmware loads in validation testing.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Applies to all desktop platforms with Intel 13th Gen CPUs.</t>
+          <t>MUST</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Standby power consumption ≤ 0.5W in deep sleep.</t>
+          <t>All firmware images and bootloader components.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Standby power consumption ≤ 0.3W.</t>
+          <t>Firmware</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>Firmware Update – Secure Boot Enforcement</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Priya Desai</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Enforce secure boot in firmware to ensure only signed and verified firmware images are loaded during device startup.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Prevents unauthorized firmware from running, protecting devices from security threats and tampering.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Enhanced device security and compliance with enterprise security standards.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Firmware updates and boot process should remain transparent to end users.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Victoria</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Intel 13th Gen CPU firmware support; power delivery subsystem</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Platform Power Team; Intel</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Firmware signing infrastructure; bootloader update capability</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Security team; Firmware engineering</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Firmware Logging – Expand Event Log Capacity</t>
-        </is>
+      <c r="A4" t="n">
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alex Chen</t>
+          <t>Rahul Singh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diagnostics</t>
+          <t>Networking</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Increase firmware event log capacity from 128 to 512 entries.</t>
+          <t>Generate downloadable audit reports</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enables better post-mortem analysis and reduces lost diagnostic data.</t>
+          <t>Improve transparency</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Improved support experience and faster root cause analysis.</t>
+          <t>Device can obtain and use an IPv6 address for basic network operations.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Technicians should always have access to recent event history.</t>
+          <t>Full IPv6 feature parity with existing IPv4 implementation.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>All commercial platforms shipping in 2024 and beyond.</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Firmware event log supports at least 512 entries.</t>
+          <t>Firmware network stack and related connectivity modules.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>No event loss during typical 3-month usage window.</t>
+          <t>Firmware</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>Network Stack – IPv6 Support in Firmware</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Add IPv6 protocol support to the firmware network stack to enable connectivity in modern network environments.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Ensures device compatibility with current and future network infrastructures.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Broader market applicability and future-proofing of device connectivity.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Network connectivity should be seamless for both IPv4 and IPv6 networks.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Victoria</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Firmware storage allocation; event log parser updates</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Diagnostics Team; Firmware Storage Team</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>WANT</t>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Network stack modules; IPv6 test infrastructure</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Networking team; Firmware QA</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="A5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pooja Mehta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Integrate system with CRM platform</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Improve customer data visibility</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Daily sync</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Real-time sync</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="A6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please update if needed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Increase heal rate if it is not 90% or higher</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Improve robustness of gate handoff to prevent breakage or deformation during paper jam events. Target for LP1.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20220315 (Sau Pin): Design Changed aligned and released for LP1 testing 20210607 (Jeffrey/TH): Under investigation, budget catered make proto to verify new design. Close up the slot, similar to sayan. Stronger piece. Target for LP1.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Better than current Manhattan units.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="A8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Implement paper de-skew function so printer can correct skewed paper during pick and guide media to a straight path.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>202200316(SP): This is already in current Manhattan product.No change to Marconi program When Paper is skewed during pick, printer can move the media in and out and guide the media to a straight path into the paper path (Normal and Best)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>as per current Manhattan, Turn roller deskew and Feed roller deskew</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>WANT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="A9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Printer must achieve minimum 30,000 pages duty cycle, goal 50,000 pages for Marconi Hi.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20221129(SP/ZJ): XXL supplies confirmed. No impact to Duty Cycle. change status to Green 20220926(Sau Pin): With XL supplies removed, page yield will reduce and will impact duty cycle numbers 20220316(SP): No Change from Manhattan 20210702 (Mandy, Jeffrey): Review when LP1 result available (w/o HW change, test more than predecessor) Waste ink is the bottleneck. We cannot do more than 30k in a month, ink will flow out. 20211011 (Jeffrey): Based on aligned mech lift with Waka Marconi Hi PDL will be about 30K, therefore accept Threshold</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Min 30,000 pages, goal 50,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="A10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The printer must withstand tilting left and right at 20 degrees while printing for a minimum of 25,000 pages, with a goal of 30,000 pages, without functional failure.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tilt 20 degree is for CISS product as acknoledged by Michelle. Shin to check if want to evaluate on Manhattan Plus with XXL ink cartridges. Close for Marconi. Threshold should be manhattan base 20k, waste ink for manhattan base is 20k in a month. Based on aligned mech life with Waka, will target 25K Duty cycle, so accept Threshold.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Min 25,000 pages</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goal 30,000 pages</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="A11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The printer must achieve a mechanical life of at least 45,000 pages (target 80,000 pages) for Marconi Base SKU while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Marconi Base LP2 DET completed and no hardware failure reported. LP1 test completed with defect investigation on-going. aerosol test in progress.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>45,000 pages</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>80,000 pages</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Firmware Update – Add Secure Boot Support</t>
-        </is>
+      <c r="A12" t="n">
+        <v>22</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Itsushi Wakabayashi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Power Management</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>The printer should support an output paper tray capacity of 100 sheets for both Marconi Base and Marconi Hi SKUs while tilted left and right at 20 degrees during printing.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Output Management Test with LP2 Life Test units show same performance as Manhattan. Need to review Marconi Base LP1 testing result. Need to conduct RnD validation test for Base SKU to support up to 80 sheets. Manhattan Base can accommodate around 80 sheets without ME modification. To align with marketing to test up to 80 on Marconi Base.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Device enters adaptive sleep within 5 minutes of inactivity and resumes in under 2 seconds.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Device enters adaptive sleep within 3 minutes of inactivity and resumes in under 1 second.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Firmware-level power state management for all supported device models.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Firmware Power Management – Adaptive Sleep Mode</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>Alex Kim</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Implement Secure Boot functionality in the firmware to ensure only signed and trusted firmware images are executed during the boot process.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Addresses increasing security threats and aligns with industry standards for device integrity.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Reduces risk of unauthorized firmware execution, improves compliance posture, and increases customer trust.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>End users should not notice any change in boot experience unless an unauthorized firmware is detected, in which case a clear error message is displayed.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Applies to all new platforms launching with Victoria and any existing platforms that can support Secure Boot via firmware update.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Secure Boot enabled by default on all supported platforms; blocks unsigned firmware.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Zero unsigned firmware allowed to execute; error handling for failed verification.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Implement an adaptive sleep mode in firmware that dynamically adjusts power states based on device usage patterns to optimize energy consumption.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Reduces overall power consumption, supporting sustainability goals and extending device lifespan.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Lower energy costs for users and improved device reliability due to reduced thermal stress.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Device should seamlessly enter and exit sleep mode without noticeable delay or impact to user workflows.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Victoria</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Platform hardware support for Secure Boot; signed firmware image infrastructure.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Security Architecture; Platform Firmware Team; Manufacturing</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>MUST</t>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Device usage analytics module; hardware power state support</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Firmware team; Hardware engineering</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Thermal Management – Adaptive Fan Control Algorithm</t>
-        </is>
+      <c r="A13" t="n">
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Mandy Hagedorn</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Assess functional failure when printer is tilted left and right at 20 degrees during printing. Follow Novelli solution for simplex and duplex print on brochure and photo media. Wider bottom margin (0.50 inch) and less ink on first side, with UI changes for media type selection.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Follow Novelli solution and align with TME and Marketing to drop this. Novelli investigated duplex on 4x6 Photo Matte media and proposed UI changes for media type selection to avoid mech limitation issues.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Device refuses to boot if firmware image signature validation fails.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Zero successful unauthorized firmware boots in validation testing.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>All firmware images loaded during device boot sequence.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Firmware Update – Secure Boot Enforcement</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>Priya Desai</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Thermal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Develop and integrate an adaptive fan control algorithm that dynamically adjusts fan speed based on real-time thermal sensor data.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Improves device reliability and user comfort by optimizing thermal performance and reducing noise.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Extends hardware lifespan, reduces RMA rates, and enhances end-user satisfaction through quieter operation.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Users should experience quieter device operation under typical workloads without thermal throttling.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>All Victoria-based platforms with active cooling systems.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Fan speed dynamically adjusts to maintain CPU temperature below 80°C under standard workloads.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Maintain CPU temperature below 75°C in 95% of use cases; minimize fan noise.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Enforce secure boot validation in firmware to ensure only signed and verified firmware images are executed during device startup.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Prevents unauthorized or malicious firmware from running, protecting device integrity and user data.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Enhanced security posture, reduced risk of firmware attacks, and compliance with industry standards.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Firmware updates and boot process should remain transparent to end users with no additional steps required.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Victoria</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Thermal sensor integration; firmware fan control module.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Thermal Engineering; Platform Firmware; Hardware Design</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Firmware signing infrastructure; secure key storage</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Security team; Firmware engineering</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ben / Ricker</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Connectivity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Remove LDV, change to 4HC. Print quality should be same as Malbec. Evaluate functional failure when printer is tilted left and right at 20 degrees during printing. Accept threshold for drop.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No change from Manhattan. Marconi has bigger swath height and printmode is more sensitive to linefeed error. LDV cannot be removed but parameter setting may be possible per vendor.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Device can obtain and use an IPv6 address for basic connectivity.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Full IPv6 feature parity with existing IPv4 implementation.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>HIGH WANT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Firmware network stack and all network-enabled features.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Network Stack – IPv6 Support</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Jordan Lee</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Add IPv6 protocol support to the device firmware network stack to enable modern network compatibility.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Ensures device operability in IPv6-only environments and future-proofs network connectivity.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Broader deployment options for enterprise and ISP customers, and compliance with emerging network standards.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Network configuration should automatically detect and utilize IPv6 where available, with no manual intervention required.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Network stack libraries; IPv6 test infrastructure</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Firmware team; Network engineering</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>30</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tracy Foo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Quality Improvement &amp; Serviceability</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PHA Rejection issue (62.80.A0): Find a fix to eliminate this issue. Workaround is to remove and re-install PHA. Monitor and implement animation prompt for re-seat as in Manhattan.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Issue reported during Manhattan launch. Root cause unknown. Animation prompt rolled out in Manhattan to reduce returns. Monitor and implement similar solution for Marconi.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Better than or equal to current Manhattan</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>High Want</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>33</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chua, Cheryl</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Environmental &amp; Sustainability compliance</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Perform IZOD Impact test if applicable when spray paint is used for EPEAT compliance.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Required for EPEAT compliance when spray paint is applied.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Required for EPEAT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>160</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>vijaya</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>The system should be fast and easy to use.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Accept - Threshold</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>inscope</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Firmware</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>EMPTY_CONVERSION</t>
         </is>
       </c>
     </row>

--- a/output/fwreq1.xlsx
+++ b/output/fwreq1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,51 +469,6 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Requestors</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>What is it?</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Strategic Importance of Solution</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Value Proposition</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Experience Intent (if any)</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Impacted Programs</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Partners</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
           <t>conversion_status</t>
         </is>
       </c>
@@ -529,7 +484,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Power Management</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -544,22 +499,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Device enters sleep mode within 2 minutes of inactivity and wakes within 5 seconds.</t>
+          <t>≤ 2.5 sec</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Device enters sleep mode within 1 minute of inactivity and wakes within 2 seconds.</t>
+          <t>≤ 2 sec</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Firmware-level power state management for all supported device models.</t>
+          <t>inscope</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -569,52 +524,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Firmware Power Management – Adaptive Sleep Mode</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Alex Kim</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Implement an adaptive sleep mode in firmware that dynamically adjusts power states based on device activity and usage patterns.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Reduces overall power consumption, extends device lifespan, and supports sustainability goals.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Lower energy costs for end users and improved device reliability through reduced wear.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Device should seamlessly enter and exit sleep mode without noticeable delay or disruption to the user.</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Device activity monitoring subsystem; hardware power state support</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Firmware team; Hardware engineering</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -644,22 +554,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Device rejects unsigned firmware images during boot.</t>
+          <t>Optional MFA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zero successful unauthorized firmware loads in validation testing.</t>
+          <t>Mandatory MFA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>All firmware images and bootloader components.</t>
+          <t>inscope</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -669,52 +579,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Firmware Update – Secure Boot Enforcement</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Priya Desai</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Enforce secure boot in firmware to ensure only signed and verified firmware images are loaded during device startup.</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Prevents unauthorized firmware from running, protecting devices from security threats and tampering.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Enhanced device security and compliance with enterprise security standards.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Firmware updates and boot process should remain transparent to end users.</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Firmware signing infrastructure; bootloader update capability</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Security team; Firmware engineering</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -729,7 +594,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Networking</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -744,22 +609,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Device can obtain and use an IPv6 address for basic network operations.</t>
+          <t>Monthly reports</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Full IPv6 feature parity with existing IPv4 implementation.</t>
+          <t>Weekly reports</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Firmware network stack and related connectivity modules.</t>
+          <t>inscope</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -769,52 +634,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Network Stack – IPv6 Support in Firmware</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Jordan Lee</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Add IPv6 protocol support to the firmware network stack to enable connectivity in modern network environments.</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Ensures device compatibility with current and future network infrastructures.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Broader market applicability and future-proofing of device connectivity.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Network connectivity should be seamless for both IPv4 and IPv6 networks.</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Network stack modules; IPv6 test infrastructure</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Networking team; Firmware QA</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -867,18 +687,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -931,18 +742,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -995,18 +797,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1059,18 +852,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1123,18 +907,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1187,18 +962,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1251,18 +1017,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1034,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Power Management</t>
+          <t>Output paper tray</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1292,22 +1049,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Device enters adaptive sleep within 5 minutes of inactivity and resumes in under 2 seconds.</t>
+          <t>100 sheets for both Marconi Base and Marconi Hi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Device enters adaptive sleep within 3 minutes of inactivity and resumes in under 1 second.</t>
+          <t>100 sheets output paper tray capacity</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH WANT</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Firmware-level power state management for all supported device models.</t>
+          <t>inscope</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,52 +1074,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Firmware Power Management – Adaptive Sleep Mode</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Alex Kim</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Implement an adaptive sleep mode in firmware that dynamically adjusts power states based on device usage patterns to optimize energy consumption.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Reduces overall power consumption, supporting sustainability goals and extending device lifespan.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Lower energy costs for users and improved device reliability due to reduced thermal stress.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Device should seamlessly enter and exit sleep mode without noticeable delay or impact to user workflows.</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Device usage analytics module; hardware power state support</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Firmware team; Hardware engineering</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1089,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1392,22 +1104,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Device refuses to boot if firmware image signature validation fails.</t>
+          <t>Accept - Threshold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zero successful unauthorized firmware boots in validation testing.</t>
+          <t>Follow Novelli solution</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Must</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>All firmware images loaded during device boot sequence.</t>
+          <t>inscope</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1417,52 +1129,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Firmware Update – Secure Boot Enforcement</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Priya Desai</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Enforce secure boot validation in firmware to ensure only signed and verified firmware images are executed during device startup.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Prevents unauthorized or malicious firmware from running, protecting device integrity and user data.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Enhanced security posture, reduced risk of firmware attacks, and compliance with industry standards.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Firmware updates and boot process should remain transparent to end users with no additional steps required.</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Firmware signing infrastructure; secure key storage</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Security team; Firmware engineering</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1144,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Connectivity</t>
+          <t>Quality Improvement &amp; Serviceability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,22 +1159,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Device can obtain and use an IPv6 address for basic connectivity.</t>
+          <t>Accept - Threshold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Full IPv6 feature parity with existing IPv4 implementation.</t>
+          <t>Same as Manhattan</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Firmware network stack and all network-enabled features.</t>
+          <t>inscope</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1517,52 +1184,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Network Stack – IPv6 Support</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Jordan Lee</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Add IPv6 protocol support to the device firmware network stack to enable modern network compatibility.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Ensures device operability in IPv6-only environments and future-proofs network connectivity.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Broader deployment options for enterprise and ISP customers, and compliance with emerging network standards.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Network configuration should automatically detect and utilize IPv6 where available, with no manual intervention required.</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Network stack libraries; IPv6 test infrastructure</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Firmware team; Network engineering</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1615,18 +1237,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1679,18 +1292,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
@@ -1735,18 +1339,9 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>EMPTY_CONVERSION</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>

--- a/output/fwreq1.xlsx
+++ b/output/fwreq1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,11 +467,6 @@
           <t>type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>conversion_status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -522,11 +517,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -577,11 +567,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -632,11 +617,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -687,11 +667,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -742,11 +717,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -797,11 +767,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -852,11 +817,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -907,11 +867,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -962,11 +917,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1017,11 +967,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1072,11 +1017,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1127,11 +1067,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1182,11 +1117,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1237,11 +1167,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1292,11 +1217,6 @@
           <t>Firmware</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1337,11 +1257,6 @@
       <c r="J17" t="inlineStr">
         <is>
           <t>Firmware</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>INVALID_CONVERSION</t>
         </is>
       </c>
     </row>
